--- a/artfynd/S 5531-2021 artfynd.xlsx
+++ b/artfynd/S 5531-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -819,6 +824,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928157</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928150</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928152</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928154</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928155</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,8 +1481,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928156</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 5531-2021 artfynd.xlsx
+++ b/artfynd/S 5531-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73928150</v>
+        <v>73928157</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>91577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Praktfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ramaria subbotrytis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Coker) Corner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oppmannaberget, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459786</v>
+        <v>459741</v>
       </c>
       <c r="R2" t="n">
-        <v>6221219</v>
+        <v>6221289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +764,22 @@
           <t>2018-11-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 fortfarande rätt fin fruktkropp.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -767,7 +788,31 @@
           <t>Bokskog</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Under bok</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Under bok</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Örjan Fritz</t>
@@ -781,16 +826,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73928150</t>
+          <t>https://artportalen.se/Sighting/73928157</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73928151</v>
+        <v>73928150</v>
       </c>
       <c r="B3" t="n">
-        <v>97785</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +843,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +867,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459796</v>
+        <v>459786</v>
       </c>
       <c r="R3" t="n">
-        <v>6221260</v>
+        <v>6221219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,11 +919,6 @@
           <t>Bokskog</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Ek</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -893,13 +933,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73928151</t>
+          <t>https://artportalen.se/Sighting/73928150</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73928152</v>
+        <v>73928151</v>
       </c>
       <c r="B4" t="n">
         <v>97785</v>
@@ -934,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459842</v>
+        <v>459796</v>
       </c>
       <c r="R4" t="n">
-        <v>6221287</v>
+        <v>6221260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +1028,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Grövre ek</t>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1005,13 +1045,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73928152</t>
+          <t>https://artportalen.se/Sighting/73928151</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73928154</v>
+        <v>73928152</v>
       </c>
       <c r="B5" t="n">
         <v>97785</v>
@@ -1046,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459819</v>
+        <v>459842</v>
       </c>
       <c r="R5" t="n">
-        <v>6221279</v>
+        <v>6221287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,6 +1138,11 @@
           <t>Bokskog</t>
         </is>
       </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Grövre ek</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1112,16 +1157,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73928154</t>
+          <t>https://artportalen.se/Sighting/73928152</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73928155</v>
+        <v>73928154</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1174,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459798</v>
+        <v>459819</v>
       </c>
       <c r="R6" t="n">
-        <v>6221355</v>
+        <v>6221279</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,16 +1264,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73928155</t>
+          <t>https://artportalen.se/Sighting/73928154</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73928156</v>
+        <v>73928155</v>
       </c>
       <c r="B7" t="n">
-        <v>44177</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459785</v>
+        <v>459798</v>
       </c>
       <c r="R7" t="n">
-        <v>6221300</v>
+        <v>6221355</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,11 +1357,6 @@
           <t>Bokskog</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bokhögstubbe</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1330,6 +1370,118 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928155</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73928156</v>
+      </c>
+      <c r="B8" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oppmannaberget, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>459785</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6221300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bokhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73928156</t>
         </is>
@@ -1343,6 +1495,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 5531-2021 artfynd.xlsx
+++ b/artfynd/S 5531-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>73928157</v>
       </c>
       <c r="B2" t="n">
-        <v>91577</v>
+        <v>91579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 5531-2021 artfynd.xlsx
+++ b/artfynd/S 5531-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>73928157</v>
       </c>
       <c r="B2" t="n">
-        <v>91579</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
